--- a/output/pdf_financials_xlsx/TVK.xlsx
+++ b/output/pdf_financials_xlsx/TVK.xlsx
@@ -4847,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>44.732</v>
+        <v>89.68600000000001</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>0.005</v>
@@ -4896,43 +4896,37 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.348</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0.334</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.955</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.144</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.427</v>
       </c>
     </row>
     <row r="93">
@@ -9479,7 +9473,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -10186,7 +10184,11 @@
           <t>Share-based payments reserve 19</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -10654,7 +10656,11 @@
           <t>Share-based payments reserve 19</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -12661,7 +12667,11 @@
           <t>Share‐based payments reserve 17</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -15738,7 +15748,11 @@
           <t>Share-based payments reserve 16</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -17166,7 +17180,11 @@
           <t>Share‐based payments reserve 16</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TVK.xlsx
+++ b/output/pdf_financials_xlsx/TVK.xlsx
@@ -1940,49 +1940,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.056</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>14.059</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>9.643000000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.569</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>9.442</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>8.359</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>9.394</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>24.758</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>28.375</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>13.946</v>
       </c>
     </row>
     <row r="35">
@@ -2044,49 +2038,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.056</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>14.059</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>9.643000000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.569</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>9.442</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>8.359</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>9.394</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>24.758</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>28.375</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>13.946</v>
       </c>
     </row>
     <row r="37">
@@ -7276,7 +7264,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13451,7 +13439,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -29324,7 +29312,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TVK.xlsx
+++ b/output/pdf_financials_xlsx/TVK.xlsx
@@ -5843,26 +5843,22 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>1.015</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>3.689</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.779</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>0.719</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -24876,7 +24872,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -26630,7 +26630,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -28672,7 +28676,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TVK.xlsx
+++ b/output/pdf_financials_xlsx/TVK.xlsx
@@ -2234,49 +2234,43 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.177</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.394</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>4.17</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>3.122</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>3.431</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>8.789</v>
       </c>
     </row>
     <row r="41">
@@ -2286,43 +2280,43 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>15.743</v>
+        <v>15.75</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>9.942</v>
+        <v>9.949</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>37.124</v>
+        <v>37.957</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>35.741</v>
+        <v>35.918</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>28.966</v>
+        <v>29.395</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>39.984</v>
+        <v>40.378</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>54.486</v>
+        <v>55.332</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>50.337</v>
+        <v>51.434</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>62.926</v>
+        <v>67.096</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>108.678</v>
+        <v>111.8</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>123.104</v>
+        <v>126.564</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>126.365</v>
+        <v>129.796</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>210.39</v>
+        <v>219.179</v>
       </c>
     </row>
     <row r="42">
@@ -3499,22 +3493,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J64" s="3" t="n">
+        <v>24.977</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>45.126</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>48.768</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>32.871</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>86.574</v>
       </c>
     </row>
     <row r="65">
@@ -3628,49 +3620,43 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>1.281</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.531</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>8.013999999999999</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>8.912000000000001</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>9.066000000000001</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.884</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>5.222</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>10.837</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>11.345</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>18.338</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>14.421</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>19.132</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>38.378</v>
       </c>
     </row>
     <row r="68">
@@ -5541,27 +5527,25 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-1.42</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>3.665</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-11.998</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-5.596</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>10.716</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.484</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>-23.16</v>
       </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
@@ -6045,35 +6029,31 @@
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.176</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H116" s="3" t="n">
+        <v>-0.075</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>-0.59</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.171</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.352</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.574</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-1.732</v>
       </c>
     </row>
     <row r="117">
@@ -20861,7 +20841,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -23922,7 +23906,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -25034,7 +25022,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -26389,7 +26381,11 @@
           <t>Changes in non‐cash operating working capital 22</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -26794,7 +26790,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -28447,7 +28447,11 @@
           <t>Changes in non-cash operating working capital 19</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -28915,7 +28919,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -31544,7 +31552,11 @@
           <t>Net changes in non‐cash operating working capital 19</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -33148,7 +33160,11 @@
           <t>Net changes in non‐cash operating working capital 18</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -34665,7 +34681,11 @@
           <t>Net changes in non‐cash operating working capital 20</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E350" s="5" t="n">
         <v>-1.42</v>
       </c>
